--- a/templates/INFRA GER ADV SR - template.xlsx
+++ b/templates/INFRA GER ADV SR - template.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$11</definedName>
@@ -1410,96 +1410,96 @@
     <row r="20" ht="15.95" customFormat="1" customHeight="1" s="30">
       <c r="B20" s="31" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C20" s="32" t="n">
-        <v>1.01247078</v>
+        <v>1.01764726</v>
       </c>
       <c r="D20" s="33" t="n">
-        <v>0.0005100920585774382</v>
+        <v>0.0005100929093093676</v>
       </c>
       <c r="E20" s="33" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F20" s="34" t="n">
-        <v>0.9399805409553909</v>
+        <v>0.9399821086556632</v>
       </c>
     </row>
     <row r="21" ht="15.95" customFormat="1" customHeight="1" s="30">
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C21" s="36" t="n">
-        <v>1.01195459</v>
+        <v>1.01712843</v>
       </c>
       <c r="D21" s="37" t="n">
-        <v>0.0005100951945022913</v>
+        <v>0.000510107195990761</v>
       </c>
       <c r="E21" s="37" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F21" s="38" t="n">
-        <v>0.9399863197325552</v>
+        <v>0.9400084356730689</v>
       </c>
     </row>
     <row r="22" ht="15.95" customFormat="1" customHeight="1" s="30">
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C22" s="36" t="n">
-        <v>1.01143866</v>
+        <v>1.01660985</v>
       </c>
       <c r="D22" s="37" t="n">
-        <v>0.0005101080994320828</v>
+        <v>0.0005100918317841874</v>
       </c>
       <c r="E22" s="37" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F22" s="38" t="n">
-        <v>0.9400101005044421</v>
+        <v>0.9399801230283931</v>
       </c>
     </row>
     <row r="23" ht="15.95" customFormat="1" customHeight="1" s="30">
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C23" s="36" t="n">
-        <v>1.01092298</v>
+        <v>1.01609155</v>
       </c>
       <c r="D23" s="37" t="n">
-        <v>0.0005100911851827483</v>
+        <v>0.0005100960146153799</v>
       </c>
       <c r="E23" s="37" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F23" s="38" t="n">
-        <v>0.9399789314929433</v>
+        <v>0.9399878310094545</v>
       </c>
     </row>
     <row r="24" ht="15.95" customFormat="1" customHeight="1" s="30">
       <c r="B24" s="35" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C24" s="36" t="n">
-        <v>1.01040758</v>
+        <v>1.01557351</v>
       </c>
       <c r="D24" s="37" t="n">
-        <v>0.0005101038335340036</v>
+        <v>0.000510100071057229</v>
       </c>
       <c r="E24" s="37" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F24" s="38" t="n">
-        <v>0.9400022394505074</v>
+        <v>0.9399953060844719</v>
       </c>
     </row>
     <row r="25" ht="15.95" customHeight="1">
@@ -1539,18 +1539,18 @@
     <row r="27" ht="15.95" customFormat="1" customHeight="1" s="30">
       <c r="B27" s="51" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C27" s="51" t="inlineStr"/>
       <c r="D27" s="37" t="n">
-        <v>0.009851387078141149</v>
+        <v>0.003576158820227882</v>
       </c>
       <c r="E27" s="37" t="n">
-        <v>0.01048336746569301</v>
+        <v>0.003804826246388782</v>
       </c>
       <c r="F27" s="38" t="n">
-        <v>0.939715898577435</v>
+        <v>0.9399006915551185</v>
       </c>
       <c r="G27" s="53" t="n"/>
     </row>
@@ -1562,13 +1562,13 @@
       </c>
       <c r="C28" s="51" t="inlineStr"/>
       <c r="D28" s="37" t="n">
-        <v>0.01089833774462146</v>
+        <v>0.01081619448217519</v>
       </c>
       <c r="E28" s="37" t="n">
-        <v>0.01159785506263344</v>
+        <v>0.0115104208368324</v>
       </c>
       <c r="F28" s="38" t="n">
-        <v>0.9396856302967841</v>
+        <v>0.9396871439803708</v>
       </c>
       <c r="G28" s="53" t="n"/>
     </row>
@@ -1580,13 +1580,13 @@
       </c>
       <c r="C29" s="39" t="inlineStr"/>
       <c r="D29" s="37" t="n">
-        <v>0.0124707799999999</v>
+        <v>0.01764725999999994</v>
       </c>
       <c r="E29" s="37" t="n">
-        <v>0.01327189162505582</v>
+        <v>0.01878398381837676</v>
       </c>
       <c r="F29" s="38" t="n">
-        <v>0.9396384744776314</v>
+        <v>0.9394844123926077</v>
       </c>
       <c r="G29" s="40" t="n"/>
     </row>
@@ -1598,13 +1598,13 @@
       </c>
       <c r="C30" s="39" t="inlineStr"/>
       <c r="D30" s="37" t="n">
-        <v>0.0124707799999999</v>
+        <v>0.01764725999999994</v>
       </c>
       <c r="E30" s="37" t="n">
-        <v>0.01327189162505582</v>
+        <v>0.01878398381837676</v>
       </c>
       <c r="F30" s="38" t="n">
-        <v>0.9396384744776314</v>
+        <v>0.9394844123926077</v>
       </c>
       <c r="G30" s="40" t="n"/>
     </row>
@@ -1632,7 +1632,7 @@
       <c r="C33" s="11" t="n"/>
       <c r="D33" s="11" t="n"/>
       <c r="E33" s="41" t="n">
-        <v>190308534.67</v>
+        <v>257721757.04</v>
       </c>
       <c r="F33" s="25" t="n"/>
       <c r="G33" s="3" t="n"/>
@@ -1647,7 +1647,7 @@
       <c r="C34" s="11" t="n"/>
       <c r="D34" s="11" t="n"/>
       <c r="E34" s="41" t="n">
-        <v>119124347.7388</v>
+        <v>149224605.2185714</v>
       </c>
       <c r="F34" s="25" t="n"/>
       <c r="G34" s="3" t="n"/>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="C36" s="16" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="D36" s="17" t="n"/>
